--- a/LEARNING/Articulation/New Microsoft Excel Worksheet.xlsx
+++ b/LEARNING/Articulation/New Microsoft Excel Worksheet.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/LEARNING/Articulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F88B81E9-085F-4DCF-BF6C-EA989AD5BED4}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7563414-5A1B-430C-85C1-4F8666DFE6F2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>I think maybe we should proceed with</t>
   </si>
@@ -55,6 +66,27 @@
   </si>
   <si>
     <t>I think I can nail this but I would like your eye on</t>
+  </si>
+  <si>
+    <t>I understand your point. I'd like to finish my explanation before we decide.</t>
+  </si>
+  <si>
+    <t>Let's take turns so we don't miss each other's points</t>
+  </si>
+  <si>
+    <t>to a Colleague</t>
+  </si>
+  <si>
+    <t>to a Manager</t>
+  </si>
+  <si>
+    <t>I appreciate your concerns. If I can finish explaining the solution, I think it will address several of the points you've raised</t>
+  </si>
+  <si>
+    <t>to a Client</t>
+  </si>
+  <si>
+    <t>I'm happy to continue once we're both able to speak without interrupting each other</t>
   </si>
 </sst>
 </file>
@@ -90,13 +122,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -378,30 +416,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -409,20 +447,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/LEARNING/Articulation/New Microsoft Excel Worksheet.xlsx
+++ b/LEARNING/Articulation/New Microsoft Excel Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/LEARNING/Articulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7563414-5A1B-430C-85C1-4F8666DFE6F2}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_F25DC773A252ABDACC104860B99F5E005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B11CEB4B-2024-4706-AA08-63F97F8CBBE2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>I think maybe we should proceed with</t>
   </si>
@@ -87,6 +87,33 @@
   </si>
   <si>
     <t>I'm happy to continue once we're both able to speak without interrupting each other</t>
+  </si>
+  <si>
+    <t>Sorry, Can I just add something to your points</t>
+  </si>
+  <si>
+    <t>I would like to build on that note…</t>
+  </si>
+  <si>
+    <t>is it ok if i…</t>
+  </si>
+  <si>
+    <t>I am going to….</t>
+  </si>
+  <si>
+    <t>This may be a silly question, how can we implement with this approach</t>
+  </si>
+  <si>
+    <t>Here's my perspective on this…</t>
+  </si>
+  <si>
+    <t>Does that make Sense… pause for few seconds … Any Questions on that ?</t>
+  </si>
+  <si>
+    <t>Never Mind. Forget it</t>
+  </si>
+  <si>
+    <t>Slow down, then finish the thought</t>
   </si>
 </sst>
 </file>
@@ -463,6 +490,43 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>11</v>
